--- a/events-results/event-registrations.xlsx
+++ b/events-results/event-registrations.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_registrations" sheetId="1" r:id="R0f40e8f27e914c85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" r:id="R7bbf86e82c124640"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_registrations" sheetId="1" r:id="Rbf0104d5bd7d4cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" r:id="Rca019f8bcad34460"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -400,7 +400,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b5e6a47a1674454"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5c5fbfcd5e3d4258"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -410,9 +410,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="eventregistrationsExport" displayName="eventregistrationsExport" ref="A1:I518" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I518"/>
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="eventregistrationsExport" displayName="eventregistrationsExport" ref="A1:H518" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H518"/>
+  <x:tableColumns count="8">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="event_id"/>
     <x:tableColumn id="3" name="event_name"/>
@@ -421,7 +421,6 @@
     <x:tableColumn id="6" name="registration_channel"/>
     <x:tableColumn id="7" name="age"/>
     <x:tableColumn id="8" name="city"/>
-    <x:tableColumn id="9" name="data_origin"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -633,7 +632,6 @@
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -658,11 +656,8 @@
       <x:c r="G1" s="9" t="str">
         <x:v>age</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>city</x:v>
-      </x:c>
-      <x:c r="I1" s="10" t="str">
-        <x:v>data_origin</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
@@ -690,9 +685,6 @@
       <x:c r="H2" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -719,9 +711,6 @@
       <x:c r="H3" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="3" t="str">
@@ -748,9 +737,6 @@
       <x:c r="H4" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -777,9 +763,6 @@
       <x:c r="H5" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="3" t="str">
@@ -806,9 +789,6 @@
       <x:c r="H6" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
       <x:c r="A7" s="3" t="str">
@@ -835,9 +815,6 @@
       <x:c r="H7" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I7" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="3" t="str">
@@ -864,9 +841,6 @@
       <x:c r="H8" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="3" t="str">
@@ -893,9 +867,6 @@
       <x:c r="H9" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
       <x:c r="A10" s="3" t="str">
@@ -922,9 +893,6 @@
       <x:c r="H10" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="3" t="str">
@@ -951,9 +919,6 @@
       <x:c r="H11" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I11" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="3" t="str">
@@ -980,9 +945,6 @@
       <x:c r="H12" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I12" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
       <x:c r="A13" s="3" t="str">
@@ -1009,9 +971,6 @@
       <x:c r="H13" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I13" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
       <x:c r="A14" s="3" t="str">
@@ -1038,9 +997,6 @@
       <x:c r="H14" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="3" t="str">
@@ -1067,9 +1023,6 @@
       <x:c r="H15" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
       <x:c r="A16" s="3" t="str">
@@ -1096,9 +1049,6 @@
       <x:c r="H16" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I16" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="3" t="str">
@@ -1125,9 +1075,6 @@
       <x:c r="H17" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I17" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
       <x:c r="A18" s="3" t="str">
@@ -1154,9 +1101,6 @@
       <x:c r="H18" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I18" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="3" t="str">
@@ -1183,9 +1127,6 @@
       <x:c r="H19" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I19" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="3" t="str">
@@ -1212,9 +1153,6 @@
       <x:c r="H20" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I20" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
       <x:c r="A21" s="3" t="str">
@@ -1241,9 +1179,6 @@
       <x:c r="H21" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I21" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
       <x:c r="A22" s="3" t="str">
@@ -1270,9 +1205,6 @@
       <x:c r="H22" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I22" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="3" t="str">
@@ -1299,9 +1231,6 @@
       <x:c r="H23" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I23" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
       <x:c r="A24" s="3" t="str">
@@ -1328,9 +1257,6 @@
       <x:c r="H24" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I24" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
       <x:c r="A25" s="3" t="str">
@@ -1357,9 +1283,6 @@
       <x:c r="H25" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I25" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
       <x:c r="A26" s="3" t="str">
@@ -1386,9 +1309,6 @@
       <x:c r="H26" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I26" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="3" t="str">
@@ -1415,9 +1335,6 @@
       <x:c r="H27" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I27" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
       <x:c r="A28" s="3" t="str">
@@ -1444,9 +1361,6 @@
       <x:c r="H28" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I28" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
       <x:c r="A29" s="3" t="str">
@@ -1473,9 +1387,6 @@
       <x:c r="H29" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I29" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="30" ht="23" customHeight="1">
       <x:c r="A30" s="3" t="str">
@@ -1502,9 +1413,6 @@
       <x:c r="H30" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I30" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="31" ht="23" customHeight="1">
       <x:c r="A31" s="3" t="str">
@@ -1531,9 +1439,6 @@
       <x:c r="H31" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I31" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="32" ht="23" customHeight="1">
       <x:c r="A32" s="3" t="str">
@@ -1560,9 +1465,6 @@
       <x:c r="H32" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I32" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="33" ht="23" customHeight="1">
       <x:c r="A33" s="3" t="str">
@@ -1589,9 +1491,6 @@
       <x:c r="H33" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I33" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="34" ht="23" customHeight="1">
       <x:c r="A34" s="3" t="str">
@@ -1618,9 +1517,6 @@
       <x:c r="H34" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I34" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="35" ht="23" customHeight="1">
       <x:c r="A35" s="3" t="str">
@@ -1647,9 +1543,6 @@
       <x:c r="H35" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I35" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="3" t="str">
@@ -1676,9 +1569,6 @@
       <x:c r="H36" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I36" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="37" ht="23" customHeight="1">
       <x:c r="A37" s="3" t="str">
@@ -1705,9 +1595,6 @@
       <x:c r="H37" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I37" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="38" ht="23" customHeight="1">
       <x:c r="A38" s="3" t="str">
@@ -1734,9 +1621,6 @@
       <x:c r="H38" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I38" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="39" ht="23" customHeight="1">
       <x:c r="A39" s="3" t="str">
@@ -1763,9 +1647,6 @@
       <x:c r="H39" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I39" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="40" ht="23" customHeight="1">
       <x:c r="A40" s="3" t="str">
@@ -1792,9 +1673,6 @@
       <x:c r="H40" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I40" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="41" ht="23" customHeight="1">
       <x:c r="A41" s="3" t="str">
@@ -1821,9 +1699,6 @@
       <x:c r="H41" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I41" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="42" ht="23" customHeight="1">
       <x:c r="A42" s="3" t="str">
@@ -1850,9 +1725,6 @@
       <x:c r="H42" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I42" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="43" ht="23" customHeight="1">
       <x:c r="A43" s="3" t="str">
@@ -1879,9 +1751,6 @@
       <x:c r="H43" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I43" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="44" ht="23" customHeight="1">
       <x:c r="A44" s="3" t="str">
@@ -1908,9 +1777,6 @@
       <x:c r="H44" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I44" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="45" ht="23" customHeight="1">
       <x:c r="A45" s="3" t="str">
@@ -1937,9 +1803,6 @@
       <x:c r="H45" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I45" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="46" ht="23" customHeight="1">
       <x:c r="A46" s="3" t="str">
@@ -1966,9 +1829,6 @@
       <x:c r="H46" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I46" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="47" ht="23" customHeight="1">
       <x:c r="A47" s="3" t="str">
@@ -1995,9 +1855,6 @@
       <x:c r="H47" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I47" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="48" ht="23" customHeight="1">
       <x:c r="A48" s="3" t="str">
@@ -2024,9 +1881,6 @@
       <x:c r="H48" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I48" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="49" ht="23" customHeight="1">
       <x:c r="A49" s="3" t="str">
@@ -2053,9 +1907,6 @@
       <x:c r="H49" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I49" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="50" ht="23" customHeight="1">
       <x:c r="A50" s="3" t="str">
@@ -2082,9 +1933,6 @@
       <x:c r="H50" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I50" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="51" ht="23" customHeight="1">
       <x:c r="A51" s="3" t="str">
@@ -2111,9 +1959,6 @@
       <x:c r="H51" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I51" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="52" ht="23" customHeight="1">
       <x:c r="A52" s="3" t="str">
@@ -2140,9 +1985,6 @@
       <x:c r="H52" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I52" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="53" ht="23" customHeight="1">
       <x:c r="A53" s="3" t="str">
@@ -2169,9 +2011,6 @@
       <x:c r="H53" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I53" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="54" ht="23" customHeight="1">
       <x:c r="A54" s="3" t="str">
@@ -2198,9 +2037,6 @@
       <x:c r="H54" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I54" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="55" ht="23" customHeight="1">
       <x:c r="A55" s="3" t="str">
@@ -2227,9 +2063,6 @@
       <x:c r="H55" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I55" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="56" ht="23" customHeight="1">
       <x:c r="A56" s="3" t="str">
@@ -2256,9 +2089,6 @@
       <x:c r="H56" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I56" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="57" ht="23" customHeight="1">
       <x:c r="A57" s="3" t="str">
@@ -2285,9 +2115,6 @@
       <x:c r="H57" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I57" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="58" ht="23" customHeight="1">
       <x:c r="A58" s="3" t="str">
@@ -2314,9 +2141,6 @@
       <x:c r="H58" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I58" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="59" ht="23" customHeight="1">
       <x:c r="A59" s="3" t="str">
@@ -2343,9 +2167,6 @@
       <x:c r="H59" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I59" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="60" ht="23" customHeight="1">
       <x:c r="A60" s="3" t="str">
@@ -2372,9 +2193,6 @@
       <x:c r="H60" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I60" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="61" ht="23" customHeight="1">
       <x:c r="A61" s="3" t="str">
@@ -2401,9 +2219,6 @@
       <x:c r="H61" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I61" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="62" ht="23" customHeight="1">
       <x:c r="A62" s="3" t="str">
@@ -2430,9 +2245,6 @@
       <x:c r="H62" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I62" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="63" ht="23" customHeight="1">
       <x:c r="A63" s="3" t="str">
@@ -2459,9 +2271,6 @@
       <x:c r="H63" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I63" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="64" ht="23" customHeight="1">
       <x:c r="A64" s="3" t="str">
@@ -2488,9 +2297,6 @@
       <x:c r="H64" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I64" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="65" ht="23" customHeight="1">
       <x:c r="A65" s="3" t="str">
@@ -2517,9 +2323,6 @@
       <x:c r="H65" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I65" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="66" ht="23" customHeight="1">
       <x:c r="A66" s="3" t="str">
@@ -2546,9 +2349,6 @@
       <x:c r="H66" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I66" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="67" ht="23" customHeight="1">
       <x:c r="A67" s="3" t="str">
@@ -2575,9 +2375,6 @@
       <x:c r="H67" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I67" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="68" ht="23" customHeight="1">
       <x:c r="A68" s="3" t="str">
@@ -2604,9 +2401,6 @@
       <x:c r="H68" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I68" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="69" ht="23" customHeight="1">
       <x:c r="A69" s="3" t="str">
@@ -2633,9 +2427,6 @@
       <x:c r="H69" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I69" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="70" ht="23" customHeight="1">
       <x:c r="A70" s="3" t="str">
@@ -2662,9 +2453,6 @@
       <x:c r="H70" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I70" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="71" ht="23" customHeight="1">
       <x:c r="A71" s="3" t="str">
@@ -2691,9 +2479,6 @@
       <x:c r="H71" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I71" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="72" ht="23" customHeight="1">
       <x:c r="A72" s="3" t="str">
@@ -2720,9 +2505,6 @@
       <x:c r="H72" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I72" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="73" ht="23" customHeight="1">
       <x:c r="A73" s="3" t="str">
@@ -2749,9 +2531,6 @@
       <x:c r="H73" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I73" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="74" ht="23" customHeight="1">
       <x:c r="A74" s="3" t="str">
@@ -2778,9 +2557,6 @@
       <x:c r="H74" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I74" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="75" ht="23" customHeight="1">
       <x:c r="A75" s="3" t="str">
@@ -2807,9 +2583,6 @@
       <x:c r="H75" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I75" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="76" ht="23" customHeight="1">
       <x:c r="A76" s="3" t="str">
@@ -2836,9 +2609,6 @@
       <x:c r="H76" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I76" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="77" ht="23" customHeight="1">
       <x:c r="A77" s="3" t="str">
@@ -2865,9 +2635,6 @@
       <x:c r="H77" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I77" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="78" ht="23" customHeight="1">
       <x:c r="A78" s="3" t="str">
@@ -2894,9 +2661,6 @@
       <x:c r="H78" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I78" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="79" ht="23" customHeight="1">
       <x:c r="A79" s="3" t="str">
@@ -2923,9 +2687,6 @@
       <x:c r="H79" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I79" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="80" ht="23" customHeight="1">
       <x:c r="A80" s="3" t="str">
@@ -2952,9 +2713,6 @@
       <x:c r="H80" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I80" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="81" ht="23" customHeight="1">
       <x:c r="A81" s="3" t="str">
@@ -2981,9 +2739,6 @@
       <x:c r="H81" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I81" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="82" ht="23" customHeight="1">
       <x:c r="A82" s="3" t="str">
@@ -3010,9 +2765,6 @@
       <x:c r="H82" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I82" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="83" ht="23" customHeight="1">
       <x:c r="A83" s="3" t="str">
@@ -3039,9 +2791,6 @@
       <x:c r="H83" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I83" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="84" ht="23" customHeight="1">
       <x:c r="A84" s="3" t="str">
@@ -3068,9 +2817,6 @@
       <x:c r="H84" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I84" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="85" ht="23" customHeight="1">
       <x:c r="A85" s="3" t="str">
@@ -3097,9 +2843,6 @@
       <x:c r="H85" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I85" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="86" ht="23" customHeight="1">
       <x:c r="A86" s="3" t="str">
@@ -3126,9 +2869,6 @@
       <x:c r="H86" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I86" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="87" ht="23" customHeight="1">
       <x:c r="A87" s="3" t="str">
@@ -3155,9 +2895,6 @@
       <x:c r="H87" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I87" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="88" ht="23" customHeight="1">
       <x:c r="A88" s="3" t="str">
@@ -3184,9 +2921,6 @@
       <x:c r="H88" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I88" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="89" ht="23" customHeight="1">
       <x:c r="A89" s="3" t="str">
@@ -3213,9 +2947,6 @@
       <x:c r="H89" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I89" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="90" ht="23" customHeight="1">
       <x:c r="A90" s="3" t="str">
@@ -3242,9 +2973,6 @@
       <x:c r="H90" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I90" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="91" ht="23" customHeight="1">
       <x:c r="A91" s="3" t="str">
@@ -3271,9 +2999,6 @@
       <x:c r="H91" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I91" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="92" ht="23" customHeight="1">
       <x:c r="A92" s="3" t="str">
@@ -3300,9 +3025,6 @@
       <x:c r="H92" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I92" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="93" ht="23" customHeight="1">
       <x:c r="A93" s="3" t="str">
@@ -3329,9 +3051,6 @@
       <x:c r="H93" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I93" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="94" ht="23" customHeight="1">
       <x:c r="A94" s="3" t="str">
@@ -3358,9 +3077,6 @@
       <x:c r="H94" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I94" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="95" ht="23" customHeight="1">
       <x:c r="A95" s="3" t="str">
@@ -3387,9 +3103,6 @@
       <x:c r="H95" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I95" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="96" ht="23" customHeight="1">
       <x:c r="A96" s="3" t="str">
@@ -3416,9 +3129,6 @@
       <x:c r="H96" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I96" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="97" ht="23" customHeight="1">
       <x:c r="A97" s="3" t="str">
@@ -3445,9 +3155,6 @@
       <x:c r="H97" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I97" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="98" ht="23" customHeight="1">
       <x:c r="A98" s="3" t="str">
@@ -3474,9 +3181,6 @@
       <x:c r="H98" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I98" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="99" ht="23" customHeight="1">
       <x:c r="A99" s="3" t="str">
@@ -3503,9 +3207,6 @@
       <x:c r="H99" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I99" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="100" ht="23" customHeight="1">
       <x:c r="A100" s="3" t="str">
@@ -3532,9 +3233,6 @@
       <x:c r="H100" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I100" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="101" ht="23" customHeight="1">
       <x:c r="A101" s="3" t="str">
@@ -3561,9 +3259,6 @@
       <x:c r="H101" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I101" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="102" ht="23" customHeight="1">
       <x:c r="A102" s="3" t="str">
@@ -3590,9 +3285,6 @@
       <x:c r="H102" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I102" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="103" ht="23" customHeight="1">
       <x:c r="A103" s="3" t="str">
@@ -3619,9 +3311,6 @@
       <x:c r="H103" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I103" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="104" ht="23" customHeight="1">
       <x:c r="A104" s="3" t="str">
@@ -3648,9 +3337,6 @@
       <x:c r="H104" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I104" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="105" ht="23" customHeight="1">
       <x:c r="A105" s="3" t="str">
@@ -3677,9 +3363,6 @@
       <x:c r="H105" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I105" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="106" ht="23" customHeight="1">
       <x:c r="A106" s="3" t="str">
@@ -3706,9 +3389,6 @@
       <x:c r="H106" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I106" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="107" ht="23" customHeight="1">
       <x:c r="A107" s="3" t="str">
@@ -3735,9 +3415,6 @@
       <x:c r="H107" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I107" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="108" ht="23" customHeight="1">
       <x:c r="A108" s="3" t="str">
@@ -3764,9 +3441,6 @@
       <x:c r="H108" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I108" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="109" ht="23" customHeight="1">
       <x:c r="A109" s="3" t="str">
@@ -3793,9 +3467,6 @@
       <x:c r="H109" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I109" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="110" ht="23" customHeight="1">
       <x:c r="A110" s="3" t="str">
@@ -3822,9 +3493,6 @@
       <x:c r="H110" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I110" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="111" ht="23" customHeight="1">
       <x:c r="A111" s="3" t="str">
@@ -3851,9 +3519,6 @@
       <x:c r="H111" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I111" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="112" ht="23" customHeight="1">
       <x:c r="A112" s="3" t="str">
@@ -3880,9 +3545,6 @@
       <x:c r="H112" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I112" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="113" ht="23" customHeight="1">
       <x:c r="A113" s="3" t="str">
@@ -3909,9 +3571,6 @@
       <x:c r="H113" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I113" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="114" ht="23" customHeight="1">
       <x:c r="A114" s="3" t="str">
@@ -3938,9 +3597,6 @@
       <x:c r="H114" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I114" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="115" ht="23" customHeight="1">
       <x:c r="A115" s="3" t="str">
@@ -3967,9 +3623,6 @@
       <x:c r="H115" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I115" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="116" ht="23" customHeight="1">
       <x:c r="A116" s="3" t="str">
@@ -3996,9 +3649,6 @@
       <x:c r="H116" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I116" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="117" ht="23" customHeight="1">
       <x:c r="A117" s="3" t="str">
@@ -4025,9 +3675,6 @@
       <x:c r="H117" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I117" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="118" ht="23" customHeight="1">
       <x:c r="A118" s="3" t="str">
@@ -4054,9 +3701,6 @@
       <x:c r="H118" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I118" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="119" ht="23" customHeight="1">
       <x:c r="A119" s="3" t="str">
@@ -4083,9 +3727,6 @@
       <x:c r="H119" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I119" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="120" ht="23" customHeight="1">
       <x:c r="A120" s="3" t="str">
@@ -4112,9 +3753,6 @@
       <x:c r="H120" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I120" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="121" ht="23" customHeight="1">
       <x:c r="A121" s="3" t="str">
@@ -4141,9 +3779,6 @@
       <x:c r="H121" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I121" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="122" ht="23" customHeight="1">
       <x:c r="A122" s="3" t="str">
@@ -4170,9 +3805,6 @@
       <x:c r="H122" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I122" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="123" ht="23" customHeight="1">
       <x:c r="A123" s="3" t="str">
@@ -4199,9 +3831,6 @@
       <x:c r="H123" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I123" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="124" ht="23" customHeight="1">
       <x:c r="A124" s="3" t="str">
@@ -4228,9 +3857,6 @@
       <x:c r="H124" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I124" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="125" ht="23" customHeight="1">
       <x:c r="A125" s="3" t="str">
@@ -4257,9 +3883,6 @@
       <x:c r="H125" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I125" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="126" ht="23" customHeight="1">
       <x:c r="A126" s="3" t="str">
@@ -4286,9 +3909,6 @@
       <x:c r="H126" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I126" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="127" ht="23" customHeight="1">
       <x:c r="A127" s="3" t="str">
@@ -4315,9 +3935,6 @@
       <x:c r="H127" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I127" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="128" ht="23" customHeight="1">
       <x:c r="A128" s="3" t="str">
@@ -4344,9 +3961,6 @@
       <x:c r="H128" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I128" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="129" ht="23" customHeight="1">
       <x:c r="A129" s="3" t="str">
@@ -4373,9 +3987,6 @@
       <x:c r="H129" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I129" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="130" ht="23" customHeight="1">
       <x:c r="A130" s="3" t="str">
@@ -4402,9 +4013,6 @@
       <x:c r="H130" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I130" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="131" ht="23" customHeight="1">
       <x:c r="A131" s="3" t="str">
@@ -4431,9 +4039,6 @@
       <x:c r="H131" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I131" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="132" ht="23" customHeight="1">
       <x:c r="A132" s="3" t="str">
@@ -4460,9 +4065,6 @@
       <x:c r="H132" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I132" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="133" ht="23" customHeight="1">
       <x:c r="A133" s="3" t="str">
@@ -4489,9 +4091,6 @@
       <x:c r="H133" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I133" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="134" ht="23" customHeight="1">
       <x:c r="A134" s="3" t="str">
@@ -4518,9 +4117,6 @@
       <x:c r="H134" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I134" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="135" ht="23" customHeight="1">
       <x:c r="A135" s="3" t="str">
@@ -4547,9 +4143,6 @@
       <x:c r="H135" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I135" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="136" ht="23" customHeight="1">
       <x:c r="A136" s="3" t="str">
@@ -4576,9 +4169,6 @@
       <x:c r="H136" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I136" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="137" ht="23" customHeight="1">
       <x:c r="A137" s="3" t="str">
@@ -4605,9 +4195,6 @@
       <x:c r="H137" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I137" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="138" ht="23" customHeight="1">
       <x:c r="A138" s="3" t="str">
@@ -4634,9 +4221,6 @@
       <x:c r="H138" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I138" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="139" ht="23" customHeight="1">
       <x:c r="A139" s="3" t="str">
@@ -4663,9 +4247,6 @@
       <x:c r="H139" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I139" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="140" ht="23" customHeight="1">
       <x:c r="A140" s="3" t="str">
@@ -4692,9 +4273,6 @@
       <x:c r="H140" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I140" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="141" ht="23" customHeight="1">
       <x:c r="A141" s="3" t="str">
@@ -4721,9 +4299,6 @@
       <x:c r="H141" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I141" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="142" ht="23" customHeight="1">
       <x:c r="A142" s="3" t="str">
@@ -4750,9 +4325,6 @@
       <x:c r="H142" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I142" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="143" ht="23" customHeight="1">
       <x:c r="A143" s="3" t="str">
@@ -4779,9 +4351,6 @@
       <x:c r="H143" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I143" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="144" ht="23" customHeight="1">
       <x:c r="A144" s="3" t="str">
@@ -4808,9 +4377,6 @@
       <x:c r="H144" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I144" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="145" ht="23" customHeight="1">
       <x:c r="A145" s="3" t="str">
@@ -4837,9 +4403,6 @@
       <x:c r="H145" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I145" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="146" ht="23" customHeight="1">
       <x:c r="A146" s="3" t="str">
@@ -4866,9 +4429,6 @@
       <x:c r="H146" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I146" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="147" ht="23" customHeight="1">
       <x:c r="A147" s="3" t="str">
@@ -4895,9 +4455,6 @@
       <x:c r="H147" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I147" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="148" ht="23" customHeight="1">
       <x:c r="A148" s="3" t="str">
@@ -4924,9 +4481,6 @@
       <x:c r="H148" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I148" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="149" ht="23" customHeight="1">
       <x:c r="A149" s="3" t="str">
@@ -4953,9 +4507,6 @@
       <x:c r="H149" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I149" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="150" ht="23" customHeight="1">
       <x:c r="A150" s="3" t="str">
@@ -4982,9 +4533,6 @@
       <x:c r="H150" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I150" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="151" ht="23" customHeight="1">
       <x:c r="A151" s="3" t="str">
@@ -5011,9 +4559,6 @@
       <x:c r="H151" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I151" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="152" ht="23" customHeight="1">
       <x:c r="A152" s="3" t="str">
@@ -5040,9 +4585,6 @@
       <x:c r="H152" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I152" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="153" ht="23" customHeight="1">
       <x:c r="A153" s="3" t="str">
@@ -5069,9 +4611,6 @@
       <x:c r="H153" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I153" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="154" ht="23" customHeight="1">
       <x:c r="A154" s="3" t="str">
@@ -5098,9 +4637,6 @@
       <x:c r="H154" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I154" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="155" ht="23" customHeight="1">
       <x:c r="A155" s="3" t="str">
@@ -5127,9 +4663,6 @@
       <x:c r="H155" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I155" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="156" ht="23" customHeight="1">
       <x:c r="A156" s="3" t="str">
@@ -5156,9 +4689,6 @@
       <x:c r="H156" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I156" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="157" ht="23" customHeight="1">
       <x:c r="A157" s="3" t="str">
@@ -5185,9 +4715,6 @@
       <x:c r="H157" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I157" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="158" ht="23" customHeight="1">
       <x:c r="A158" s="3" t="str">
@@ -5214,9 +4741,6 @@
       <x:c r="H158" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I158" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="159" ht="23" customHeight="1">
       <x:c r="A159" s="3" t="str">
@@ -5243,9 +4767,6 @@
       <x:c r="H159" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I159" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="160" ht="23" customHeight="1">
       <x:c r="A160" s="3" t="str">
@@ -5272,9 +4793,6 @@
       <x:c r="H160" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I160" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="161" ht="23" customHeight="1">
       <x:c r="A161" s="3" t="str">
@@ -5301,9 +4819,6 @@
       <x:c r="H161" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I161" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="162" ht="23" customHeight="1">
       <x:c r="A162" s="3" t="str">
@@ -5330,9 +4845,6 @@
       <x:c r="H162" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I162" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="163" ht="23" customHeight="1">
       <x:c r="A163" s="3" t="str">
@@ -5359,9 +4871,6 @@
       <x:c r="H163" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I163" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="164" ht="23" customHeight="1">
       <x:c r="A164" s="3" t="str">
@@ -5388,9 +4897,6 @@
       <x:c r="H164" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I164" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="165" ht="23" customHeight="1">
       <x:c r="A165" s="3" t="str">
@@ -5417,9 +4923,6 @@
       <x:c r="H165" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I165" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="166" ht="23" customHeight="1">
       <x:c r="A166" s="3" t="str">
@@ -5446,9 +4949,6 @@
       <x:c r="H166" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I166" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="167" ht="23" customHeight="1">
       <x:c r="A167" s="3" t="str">
@@ -5475,9 +4975,6 @@
       <x:c r="H167" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I167" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="168" ht="23" customHeight="1">
       <x:c r="A168" s="3" t="str">
@@ -5504,9 +5001,6 @@
       <x:c r="H168" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I168" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="169" ht="23" customHeight="1">
       <x:c r="A169" s="3" t="str">
@@ -5533,9 +5027,6 @@
       <x:c r="H169" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I169" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="170" ht="23" customHeight="1">
       <x:c r="A170" s="3" t="str">
@@ -5562,9 +5053,6 @@
       <x:c r="H170" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I170" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="171" ht="23" customHeight="1">
       <x:c r="A171" s="3" t="str">
@@ -5591,9 +5079,6 @@
       <x:c r="H171" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I171" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="172" ht="23" customHeight="1">
       <x:c r="A172" s="3" t="str">
@@ -5620,9 +5105,6 @@
       <x:c r="H172" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I172" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="173" ht="23" customHeight="1">
       <x:c r="A173" s="3" t="str">
@@ -5649,9 +5131,6 @@
       <x:c r="H173" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I173" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="174" ht="23" customHeight="1">
       <x:c r="A174" s="3" t="str">
@@ -5678,9 +5157,6 @@
       <x:c r="H174" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I174" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="175" ht="23" customHeight="1">
       <x:c r="A175" s="3" t="str">
@@ -5707,9 +5183,6 @@
       <x:c r="H175" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I175" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="176" ht="23" customHeight="1">
       <x:c r="A176" s="3" t="str">
@@ -5736,9 +5209,6 @@
       <x:c r="H176" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I176" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="177" ht="23" customHeight="1">
       <x:c r="A177" s="3" t="str">
@@ -5765,9 +5235,6 @@
       <x:c r="H177" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I177" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="178" ht="23" customHeight="1">
       <x:c r="A178" s="3" t="str">
@@ -5794,9 +5261,6 @@
       <x:c r="H178" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I178" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="179" ht="23" customHeight="1">
       <x:c r="A179" s="3" t="str">
@@ -5823,9 +5287,6 @@
       <x:c r="H179" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I179" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="180" ht="23" customHeight="1">
       <x:c r="A180" s="3" t="str">
@@ -5852,9 +5313,6 @@
       <x:c r="H180" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I180" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="181" ht="23" customHeight="1">
       <x:c r="A181" s="3" t="str">
@@ -5881,9 +5339,6 @@
       <x:c r="H181" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I181" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="182" ht="23" customHeight="1">
       <x:c r="A182" s="3" t="str">
@@ -5910,9 +5365,6 @@
       <x:c r="H182" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I182" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="183" ht="23" customHeight="1">
       <x:c r="A183" s="3" t="str">
@@ -5939,9 +5391,6 @@
       <x:c r="H183" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I183" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="184" ht="23" customHeight="1">
       <x:c r="A184" s="3" t="str">
@@ -5968,9 +5417,6 @@
       <x:c r="H184" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I184" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="185" ht="23" customHeight="1">
       <x:c r="A185" s="3" t="str">
@@ -5997,9 +5443,6 @@
       <x:c r="H185" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I185" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="186" ht="23" customHeight="1">
       <x:c r="A186" s="3" t="str">
@@ -6026,9 +5469,6 @@
       <x:c r="H186" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I186" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="187" ht="23" customHeight="1">
       <x:c r="A187" s="3" t="str">
@@ -6055,9 +5495,6 @@
       <x:c r="H187" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I187" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="188" ht="23" customHeight="1">
       <x:c r="A188" s="3" t="str">
@@ -6084,9 +5521,6 @@
       <x:c r="H188" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I188" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="189" ht="23" customHeight="1">
       <x:c r="A189" s="3" t="str">
@@ -6113,9 +5547,6 @@
       <x:c r="H189" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I189" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="190" ht="23" customHeight="1">
       <x:c r="A190" s="3" t="str">
@@ -6142,9 +5573,6 @@
       <x:c r="H190" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I190" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="191" ht="23" customHeight="1">
       <x:c r="A191" s="3" t="str">
@@ -6171,9 +5599,6 @@
       <x:c r="H191" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I191" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="192" ht="23" customHeight="1">
       <x:c r="A192" s="3" t="str">
@@ -6200,9 +5625,6 @@
       <x:c r="H192" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I192" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="193" ht="23" customHeight="1">
       <x:c r="A193" s="3" t="str">
@@ -6229,9 +5651,6 @@
       <x:c r="H193" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I193" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="194" ht="23" customHeight="1">
       <x:c r="A194" s="3" t="str">
@@ -6258,9 +5677,6 @@
       <x:c r="H194" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I194" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="195" ht="23" customHeight="1">
       <x:c r="A195" s="3" t="str">
@@ -6287,9 +5703,6 @@
       <x:c r="H195" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I195" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="196" ht="23" customHeight="1">
       <x:c r="A196" s="3" t="str">
@@ -6316,9 +5729,6 @@
       <x:c r="H196" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I196" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="197" ht="23" customHeight="1">
       <x:c r="A197" s="3" t="str">
@@ -6345,9 +5755,6 @@
       <x:c r="H197" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I197" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="198" ht="23" customHeight="1">
       <x:c r="A198" s="3" t="str">
@@ -6374,9 +5781,6 @@
       <x:c r="H198" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I198" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="199" ht="23" customHeight="1">
       <x:c r="A199" s="3" t="str">
@@ -6403,9 +5807,6 @@
       <x:c r="H199" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I199" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="200" ht="23" customHeight="1">
       <x:c r="A200" s="3" t="str">
@@ -6432,9 +5833,6 @@
       <x:c r="H200" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I200" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="201" ht="23" customHeight="1">
       <x:c r="A201" s="3" t="str">
@@ -6461,9 +5859,6 @@
       <x:c r="H201" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I201" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="202" ht="23" customHeight="1">
       <x:c r="A202" s="3" t="str">
@@ -6490,9 +5885,6 @@
       <x:c r="H202" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I202" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="203" ht="23" customHeight="1">
       <x:c r="A203" s="3" t="str">
@@ -6519,9 +5911,6 @@
       <x:c r="H203" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I203" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="204" ht="23" customHeight="1">
       <x:c r="A204" s="3" t="str">
@@ -6548,9 +5937,6 @@
       <x:c r="H204" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I204" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="205" ht="23" customHeight="1">
       <x:c r="A205" s="3" t="str">
@@ -6577,9 +5963,6 @@
       <x:c r="H205" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I205" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="206" ht="23" customHeight="1">
       <x:c r="A206" s="3" t="str">
@@ -6606,9 +5989,6 @@
       <x:c r="H206" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I206" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="207" ht="23" customHeight="1">
       <x:c r="A207" s="3" t="str">
@@ -6635,9 +6015,6 @@
       <x:c r="H207" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I207" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="208" ht="23" customHeight="1">
       <x:c r="A208" s="3" t="str">
@@ -6664,9 +6041,6 @@
       <x:c r="H208" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I208" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="209" ht="23" customHeight="1">
       <x:c r="A209" s="3" t="str">
@@ -6693,9 +6067,6 @@
       <x:c r="H209" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I209" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="210" ht="23" customHeight="1">
       <x:c r="A210" s="3" t="str">
@@ -6722,9 +6093,6 @@
       <x:c r="H210" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I210" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="211" ht="23" customHeight="1">
       <x:c r="A211" s="3" t="str">
@@ -6751,9 +6119,6 @@
       <x:c r="H211" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I211" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="212" ht="23" customHeight="1">
       <x:c r="A212" s="3" t="str">
@@ -6780,9 +6145,6 @@
       <x:c r="H212" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I212" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="213" ht="23" customHeight="1">
       <x:c r="A213" s="3" t="str">
@@ -6809,9 +6171,6 @@
       <x:c r="H213" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I213" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="214" ht="23" customHeight="1">
       <x:c r="A214" s="3" t="str">
@@ -6838,9 +6197,6 @@
       <x:c r="H214" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I214" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="215" ht="23" customHeight="1">
       <x:c r="A215" s="3" t="str">
@@ -6867,9 +6223,6 @@
       <x:c r="H215" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I215" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="216" ht="23" customHeight="1">
       <x:c r="A216" s="3" t="str">
@@ -6896,9 +6249,6 @@
       <x:c r="H216" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I216" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="217" ht="23" customHeight="1">
       <x:c r="A217" s="3" t="str">
@@ -6925,9 +6275,6 @@
       <x:c r="H217" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I217" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="218" ht="23" customHeight="1">
       <x:c r="A218" s="3" t="str">
@@ -6954,9 +6301,6 @@
       <x:c r="H218" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I218" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="219" ht="23" customHeight="1">
       <x:c r="A219" s="3" t="str">
@@ -6983,9 +6327,6 @@
       <x:c r="H219" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I219" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="220" ht="23" customHeight="1">
       <x:c r="A220" s="3" t="str">
@@ -7012,9 +6353,6 @@
       <x:c r="H220" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I220" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="221" ht="23" customHeight="1">
       <x:c r="A221" s="3" t="str">
@@ -7041,9 +6379,6 @@
       <x:c r="H221" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I221" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="222" ht="23" customHeight="1">
       <x:c r="A222" s="3" t="str">
@@ -7070,9 +6405,6 @@
       <x:c r="H222" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I222" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="223" ht="23" customHeight="1">
       <x:c r="A223" s="3" t="str">
@@ -7099,9 +6431,6 @@
       <x:c r="H223" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I223" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="224" ht="23" customHeight="1">
       <x:c r="A224" s="3" t="str">
@@ -7128,9 +6457,6 @@
       <x:c r="H224" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I224" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="225" ht="23" customHeight="1">
       <x:c r="A225" s="3" t="str">
@@ -7157,9 +6483,6 @@
       <x:c r="H225" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I225" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="226" ht="23" customHeight="1">
       <x:c r="A226" s="3" t="str">
@@ -7186,9 +6509,6 @@
       <x:c r="H226" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I226" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="227" ht="23" customHeight="1">
       <x:c r="A227" s="3" t="str">
@@ -7215,9 +6535,6 @@
       <x:c r="H227" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I227" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="228" ht="23" customHeight="1">
       <x:c r="A228" s="3" t="str">
@@ -7244,9 +6561,6 @@
       <x:c r="H228" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I228" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="229" ht="23" customHeight="1">
       <x:c r="A229" s="3" t="str">
@@ -7273,9 +6587,6 @@
       <x:c r="H229" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I229" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="230" ht="23" customHeight="1">
       <x:c r="A230" s="3" t="str">
@@ -7302,9 +6613,6 @@
       <x:c r="H230" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I230" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="231" ht="23" customHeight="1">
       <x:c r="A231" s="3" t="str">
@@ -7331,9 +6639,6 @@
       <x:c r="H231" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I231" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="232" ht="23" customHeight="1">
       <x:c r="A232" s="3" t="str">
@@ -7360,9 +6665,6 @@
       <x:c r="H232" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I232" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="233" ht="23" customHeight="1">
       <x:c r="A233" s="3" t="str">
@@ -7389,9 +6691,6 @@
       <x:c r="H233" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I233" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="234" ht="23" customHeight="1">
       <x:c r="A234" s="3" t="str">
@@ -7418,9 +6717,6 @@
       <x:c r="H234" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I234" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="235" ht="23" customHeight="1">
       <x:c r="A235" s="3" t="str">
@@ -7447,9 +6743,6 @@
       <x:c r="H235" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I235" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="236" ht="23" customHeight="1">
       <x:c r="A236" s="3" t="str">
@@ -7476,9 +6769,6 @@
       <x:c r="H236" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I236" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="237" ht="23" customHeight="1">
       <x:c r="A237" s="3" t="str">
@@ -7505,9 +6795,6 @@
       <x:c r="H237" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I237" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="238" ht="23" customHeight="1">
       <x:c r="A238" s="3" t="str">
@@ -7534,9 +6821,6 @@
       <x:c r="H238" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I238" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="239" ht="23" customHeight="1">
       <x:c r="A239" s="3" t="str">
@@ -7563,9 +6847,6 @@
       <x:c r="H239" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I239" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="240" ht="23" customHeight="1">
       <x:c r="A240" s="3" t="str">
@@ -7592,9 +6873,6 @@
       <x:c r="H240" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I240" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="241" ht="23" customHeight="1">
       <x:c r="A241" s="3" t="str">
@@ -7621,9 +6899,6 @@
       <x:c r="H241" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I241" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="242" ht="23" customHeight="1">
       <x:c r="A242" s="3" t="str">
@@ -7650,9 +6925,6 @@
       <x:c r="H242" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I242" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="243" ht="23" customHeight="1">
       <x:c r="A243" s="3" t="str">
@@ -7679,9 +6951,6 @@
       <x:c r="H243" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I243" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="244" ht="23" customHeight="1">
       <x:c r="A244" s="3" t="str">
@@ -7708,9 +6977,6 @@
       <x:c r="H244" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I244" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="245" ht="23" customHeight="1">
       <x:c r="A245" s="3" t="str">
@@ -7737,9 +7003,6 @@
       <x:c r="H245" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I245" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="246" ht="23" customHeight="1">
       <x:c r="A246" s="3" t="str">
@@ -7766,9 +7029,6 @@
       <x:c r="H246" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I246" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="247" ht="23" customHeight="1">
       <x:c r="A247" s="3" t="str">
@@ -7795,9 +7055,6 @@
       <x:c r="H247" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I247" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="248" ht="23" customHeight="1">
       <x:c r="A248" s="3" t="str">
@@ -7824,9 +7081,6 @@
       <x:c r="H248" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I248" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="249" ht="23" customHeight="1">
       <x:c r="A249" s="3" t="str">
@@ -7853,9 +7107,6 @@
       <x:c r="H249" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I249" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="250" ht="23" customHeight="1">
       <x:c r="A250" s="3" t="str">
@@ -7882,9 +7133,6 @@
       <x:c r="H250" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I250" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="251" ht="23" customHeight="1">
       <x:c r="A251" s="3" t="str">
@@ -7911,9 +7159,6 @@
       <x:c r="H251" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I251" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="252" ht="23" customHeight="1">
       <x:c r="A252" s="3" t="str">
@@ -7940,9 +7185,6 @@
       <x:c r="H252" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I252" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="253" ht="23" customHeight="1">
       <x:c r="A253" s="3" t="str">
@@ -7969,9 +7211,6 @@
       <x:c r="H253" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I253" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="254" ht="23" customHeight="1">
       <x:c r="A254" s="3" t="str">
@@ -7998,9 +7237,6 @@
       <x:c r="H254" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I254" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="255" ht="23" customHeight="1">
       <x:c r="A255" s="3" t="str">
@@ -8027,9 +7263,6 @@
       <x:c r="H255" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I255" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="256" ht="23" customHeight="1">
       <x:c r="A256" s="3" t="str">
@@ -8056,9 +7289,6 @@
       <x:c r="H256" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I256" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="257" ht="23" customHeight="1">
       <x:c r="A257" s="3" t="str">
@@ -8085,9 +7315,6 @@
       <x:c r="H257" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I257" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="258" ht="23" customHeight="1">
       <x:c r="A258" s="3" t="str">
@@ -8114,9 +7341,6 @@
       <x:c r="H258" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I258" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="259" ht="23" customHeight="1">
       <x:c r="A259" s="3" t="str">
@@ -8143,9 +7367,6 @@
       <x:c r="H259" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I259" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="260" ht="23" customHeight="1">
       <x:c r="A260" s="3" t="str">
@@ -8172,9 +7393,6 @@
       <x:c r="H260" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I260" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="261" ht="23" customHeight="1">
       <x:c r="A261" s="3" t="str">
@@ -8201,9 +7419,6 @@
       <x:c r="H261" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I261" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="262" ht="23" customHeight="1">
       <x:c r="A262" s="3" t="str">
@@ -8230,9 +7445,6 @@
       <x:c r="H262" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I262" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="263" ht="23" customHeight="1">
       <x:c r="A263" s="3" t="str">
@@ -8259,9 +7471,6 @@
       <x:c r="H263" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I263" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="264" ht="23" customHeight="1">
       <x:c r="A264" s="3" t="str">
@@ -8288,9 +7497,6 @@
       <x:c r="H264" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I264" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="265" ht="23" customHeight="1">
       <x:c r="A265" s="3" t="str">
@@ -8317,9 +7523,6 @@
       <x:c r="H265" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I265" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="266" ht="23" customHeight="1">
       <x:c r="A266" s="3" t="str">
@@ -8346,9 +7549,6 @@
       <x:c r="H266" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I266" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="267" ht="23" customHeight="1">
       <x:c r="A267" s="3" t="str">
@@ -8375,9 +7575,6 @@
       <x:c r="H267" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I267" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="268" ht="23" customHeight="1">
       <x:c r="A268" s="3" t="str">
@@ -8404,9 +7601,6 @@
       <x:c r="H268" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I268" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="269" ht="23" customHeight="1">
       <x:c r="A269" s="3" t="str">
@@ -8433,9 +7627,6 @@
       <x:c r="H269" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I269" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="270" ht="23" customHeight="1">
       <x:c r="A270" s="3" t="str">
@@ -8462,9 +7653,6 @@
       <x:c r="H270" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I270" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="271" ht="23" customHeight="1">
       <x:c r="A271" s="3" t="str">
@@ -8491,9 +7679,6 @@
       <x:c r="H271" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I271" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="272" ht="23" customHeight="1">
       <x:c r="A272" s="3" t="str">
@@ -8520,9 +7705,6 @@
       <x:c r="H272" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I272" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="273" ht="23" customHeight="1">
       <x:c r="A273" s="3" t="str">
@@ -8549,9 +7731,6 @@
       <x:c r="H273" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I273" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="274" ht="23" customHeight="1">
       <x:c r="A274" s="3" t="str">
@@ -8578,9 +7757,6 @@
       <x:c r="H274" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I274" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="275" ht="23" customHeight="1">
       <x:c r="A275" s="3" t="str">
@@ -8607,9 +7783,6 @@
       <x:c r="H275" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I275" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="276" ht="23" customHeight="1">
       <x:c r="A276" s="3" t="str">
@@ -8636,9 +7809,6 @@
       <x:c r="H276" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I276" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="277" ht="23" customHeight="1">
       <x:c r="A277" s="3" t="str">
@@ -8665,9 +7835,6 @@
       <x:c r="H277" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I277" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="278" ht="23" customHeight="1">
       <x:c r="A278" s="3" t="str">
@@ -8694,9 +7861,6 @@
       <x:c r="H278" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I278" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="279" ht="23" customHeight="1">
       <x:c r="A279" s="3" t="str">
@@ -8723,9 +7887,6 @@
       <x:c r="H279" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I279" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="280" ht="23" customHeight="1">
       <x:c r="A280" s="3" t="str">
@@ -8752,9 +7913,6 @@
       <x:c r="H280" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I280" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="281" ht="23" customHeight="1">
       <x:c r="A281" s="3" t="str">
@@ -8781,9 +7939,6 @@
       <x:c r="H281" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I281" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="282" ht="23" customHeight="1">
       <x:c r="A282" s="3" t="str">
@@ -8810,9 +7965,6 @@
       <x:c r="H282" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I282" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="283" ht="23" customHeight="1">
       <x:c r="A283" s="3" t="str">
@@ -8839,9 +7991,6 @@
       <x:c r="H283" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I283" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="284" ht="23" customHeight="1">
       <x:c r="A284" s="3" t="str">
@@ -8868,9 +8017,6 @@
       <x:c r="H284" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I284" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="285" ht="23" customHeight="1">
       <x:c r="A285" s="3" t="str">
@@ -8897,9 +8043,6 @@
       <x:c r="H285" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I285" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="286" ht="23" customHeight="1">
       <x:c r="A286" s="3" t="str">
@@ -8926,9 +8069,6 @@
       <x:c r="H286" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I286" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="287" ht="23" customHeight="1">
       <x:c r="A287" s="3" t="str">
@@ -8955,9 +8095,6 @@
       <x:c r="H287" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I287" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="288" ht="23" customHeight="1">
       <x:c r="A288" s="3" t="str">
@@ -8984,9 +8121,6 @@
       <x:c r="H288" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I288" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="289" ht="23" customHeight="1">
       <x:c r="A289" s="3" t="str">
@@ -9013,9 +8147,6 @@
       <x:c r="H289" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I289" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="290" ht="23" customHeight="1">
       <x:c r="A290" s="3" t="str">
@@ -9042,9 +8173,6 @@
       <x:c r="H290" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I290" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="291" ht="23" customHeight="1">
       <x:c r="A291" s="3" t="str">
@@ -9071,9 +8199,6 @@
       <x:c r="H291" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I291" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="292" ht="23" customHeight="1">
       <x:c r="A292" s="3" t="str">
@@ -9100,9 +8225,6 @@
       <x:c r="H292" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I292" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="293" ht="23" customHeight="1">
       <x:c r="A293" s="3" t="str">
@@ -9129,9 +8251,6 @@
       <x:c r="H293" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I293" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="294" ht="23" customHeight="1">
       <x:c r="A294" s="3" t="str">
@@ -9158,9 +8277,6 @@
       <x:c r="H294" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I294" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="295" ht="23" customHeight="1">
       <x:c r="A295" s="3" t="str">
@@ -9187,9 +8303,6 @@
       <x:c r="H295" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I295" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="296" ht="23" customHeight="1">
       <x:c r="A296" s="3" t="str">
@@ -9216,9 +8329,6 @@
       <x:c r="H296" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I296" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="297" ht="23" customHeight="1">
       <x:c r="A297" s="3" t="str">
@@ -9245,9 +8355,6 @@
       <x:c r="H297" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I297" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="298" ht="23" customHeight="1">
       <x:c r="A298" s="3" t="str">
@@ -9274,9 +8381,6 @@
       <x:c r="H298" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I298" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="299" ht="23" customHeight="1">
       <x:c r="A299" s="3" t="str">
@@ -9303,9 +8407,6 @@
       <x:c r="H299" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I299" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="300" ht="23" customHeight="1">
       <x:c r="A300" s="3" t="str">
@@ -9332,9 +8433,6 @@
       <x:c r="H300" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I300" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="301" ht="23" customHeight="1">
       <x:c r="A301" s="3" t="str">
@@ -9361,9 +8459,6 @@
       <x:c r="H301" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I301" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="302" ht="23" customHeight="1">
       <x:c r="A302" s="3" t="str">
@@ -9390,9 +8485,6 @@
       <x:c r="H302" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I302" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="303" ht="23" customHeight="1">
       <x:c r="A303" s="3" t="str">
@@ -9419,9 +8511,6 @@
       <x:c r="H303" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I303" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="304" ht="23" customHeight="1">
       <x:c r="A304" s="3" t="str">
@@ -9448,9 +8537,6 @@
       <x:c r="H304" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I304" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="305" ht="23" customHeight="1">
       <x:c r="A305" s="3" t="str">
@@ -9477,9 +8563,6 @@
       <x:c r="H305" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I305" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="306" ht="23" customHeight="1">
       <x:c r="A306" s="3" t="str">
@@ -9506,9 +8589,6 @@
       <x:c r="H306" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I306" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="307" ht="23" customHeight="1">
       <x:c r="A307" s="3" t="str">
@@ -9535,9 +8615,6 @@
       <x:c r="H307" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I307" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="308" ht="23" customHeight="1">
       <x:c r="A308" s="3" t="str">
@@ -9564,9 +8641,6 @@
       <x:c r="H308" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I308" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="309" ht="23" customHeight="1">
       <x:c r="A309" s="3" t="str">
@@ -9593,9 +8667,6 @@
       <x:c r="H309" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I309" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="310" ht="23" customHeight="1">
       <x:c r="A310" s="3" t="str">
@@ -9622,9 +8693,6 @@
       <x:c r="H310" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I310" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="311" ht="23" customHeight="1">
       <x:c r="A311" s="3" t="str">
@@ -9651,9 +8719,6 @@
       <x:c r="H311" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I311" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="312" ht="23" customHeight="1">
       <x:c r="A312" s="3" t="str">
@@ -9680,9 +8745,6 @@
       <x:c r="H312" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I312" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="313" ht="23" customHeight="1">
       <x:c r="A313" s="3" t="str">
@@ -9709,9 +8771,6 @@
       <x:c r="H313" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I313" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="314" ht="23" customHeight="1">
       <x:c r="A314" s="3" t="str">
@@ -9738,9 +8797,6 @@
       <x:c r="H314" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I314" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="315" ht="23" customHeight="1">
       <x:c r="A315" s="3" t="str">
@@ -9767,9 +8823,6 @@
       <x:c r="H315" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I315" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="316" ht="23" customHeight="1">
       <x:c r="A316" s="3" t="str">
@@ -9796,9 +8849,6 @@
       <x:c r="H316" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I316" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="317" ht="23" customHeight="1">
       <x:c r="A317" s="3" t="str">
@@ -9825,9 +8875,6 @@
       <x:c r="H317" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I317" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="318" ht="23" customHeight="1">
       <x:c r="A318" s="3" t="str">
@@ -9854,9 +8901,6 @@
       <x:c r="H318" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I318" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="319" ht="23" customHeight="1">
       <x:c r="A319" s="3" t="str">
@@ -9883,9 +8927,6 @@
       <x:c r="H319" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I319" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="320" ht="23" customHeight="1">
       <x:c r="A320" s="3" t="str">
@@ -9912,9 +8953,6 @@
       <x:c r="H320" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I320" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="321" ht="23" customHeight="1">
       <x:c r="A321" s="3" t="str">
@@ -9941,9 +8979,6 @@
       <x:c r="H321" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I321" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="322" ht="23" customHeight="1">
       <x:c r="A322" s="3" t="str">
@@ -9970,9 +9005,6 @@
       <x:c r="H322" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I322" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="323" ht="23" customHeight="1">
       <x:c r="A323" s="3" t="str">
@@ -9999,9 +9031,6 @@
       <x:c r="H323" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I323" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="324" ht="23" customHeight="1">
       <x:c r="A324" s="3" t="str">
@@ -10028,9 +9057,6 @@
       <x:c r="H324" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I324" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="325" ht="23" customHeight="1">
       <x:c r="A325" s="3" t="str">
@@ -10057,9 +9083,6 @@
       <x:c r="H325" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I325" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="326" ht="23" customHeight="1">
       <x:c r="A326" s="3" t="str">
@@ -10086,9 +9109,6 @@
       <x:c r="H326" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I326" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="327" ht="23" customHeight="1">
       <x:c r="A327" s="3" t="str">
@@ -10115,9 +9135,6 @@
       <x:c r="H327" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I327" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="328" ht="23" customHeight="1">
       <x:c r="A328" s="3" t="str">
@@ -10144,9 +9161,6 @@
       <x:c r="H328" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I328" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="329" ht="23" customHeight="1">
       <x:c r="A329" s="3" t="str">
@@ -10173,9 +9187,6 @@
       <x:c r="H329" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I329" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="330" ht="23" customHeight="1">
       <x:c r="A330" s="3" t="str">
@@ -10202,9 +9213,6 @@
       <x:c r="H330" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I330" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="331" ht="23" customHeight="1">
       <x:c r="A331" s="3" t="str">
@@ -10231,9 +9239,6 @@
       <x:c r="H331" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I331" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="332" ht="23" customHeight="1">
       <x:c r="A332" s="3" t="str">
@@ -10260,9 +9265,6 @@
       <x:c r="H332" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I332" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="333" ht="23" customHeight="1">
       <x:c r="A333" s="3" t="str">
@@ -10289,9 +9291,6 @@
       <x:c r="H333" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I333" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="334" ht="23" customHeight="1">
       <x:c r="A334" s="3" t="str">
@@ -10318,9 +9317,6 @@
       <x:c r="H334" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I334" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="335" ht="23" customHeight="1">
       <x:c r="A335" s="3" t="str">
@@ -10347,9 +9343,6 @@
       <x:c r="H335" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I335" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="336" ht="23" customHeight="1">
       <x:c r="A336" s="3" t="str">
@@ -10376,9 +9369,6 @@
       <x:c r="H336" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I336" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="337" ht="23" customHeight="1">
       <x:c r="A337" s="3" t="str">
@@ -10405,9 +9395,6 @@
       <x:c r="H337" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I337" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="338" ht="23" customHeight="1">
       <x:c r="A338" s="3" t="str">
@@ -10434,9 +9421,6 @@
       <x:c r="H338" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I338" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="339" ht="23" customHeight="1">
       <x:c r="A339" s="3" t="str">
@@ -10463,9 +9447,6 @@
       <x:c r="H339" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I339" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="340" ht="23" customHeight="1">
       <x:c r="A340" s="3" t="str">
@@ -10492,9 +9473,6 @@
       <x:c r="H340" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I340" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="341" ht="23" customHeight="1">
       <x:c r="A341" s="3" t="str">
@@ -10521,9 +9499,6 @@
       <x:c r="H341" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I341" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="342" ht="23" customHeight="1">
       <x:c r="A342" s="3" t="str">
@@ -10550,9 +9525,6 @@
       <x:c r="H342" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I342" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="343" ht="23" customHeight="1">
       <x:c r="A343" s="3" t="str">
@@ -10579,9 +9551,6 @@
       <x:c r="H343" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I343" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="344" ht="23" customHeight="1">
       <x:c r="A344" s="3" t="str">
@@ -10608,9 +9577,6 @@
       <x:c r="H344" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I344" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="345" ht="23" customHeight="1">
       <x:c r="A345" s="3" t="str">
@@ -10637,9 +9603,6 @@
       <x:c r="H345" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I345" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="346" ht="23" customHeight="1">
       <x:c r="A346" s="3" t="str">
@@ -10666,9 +9629,6 @@
       <x:c r="H346" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I346" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="347" ht="23" customHeight="1">
       <x:c r="A347" s="3" t="str">
@@ -10695,9 +9655,6 @@
       <x:c r="H347" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I347" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="348" ht="23" customHeight="1">
       <x:c r="A348" s="3" t="str">
@@ -10724,9 +9681,6 @@
       <x:c r="H348" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I348" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="349" ht="23" customHeight="1">
       <x:c r="A349" s="3" t="str">
@@ -10753,9 +9707,6 @@
       <x:c r="H349" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I349" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="350" ht="23" customHeight="1">
       <x:c r="A350" s="3" t="str">
@@ -10782,9 +9733,6 @@
       <x:c r="H350" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I350" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="351" ht="23" customHeight="1">
       <x:c r="A351" s="3" t="str">
@@ -10811,9 +9759,6 @@
       <x:c r="H351" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I351" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="352" ht="23" customHeight="1">
       <x:c r="A352" s="3" t="str">
@@ -10840,9 +9785,6 @@
       <x:c r="H352" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I352" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="353" ht="23" customHeight="1">
       <x:c r="A353" s="3" t="str">
@@ -10869,9 +9811,6 @@
       <x:c r="H353" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I353" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="354" ht="23" customHeight="1">
       <x:c r="A354" s="3" t="str">
@@ -10898,9 +9837,6 @@
       <x:c r="H354" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I354" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="355" ht="23" customHeight="1">
       <x:c r="A355" s="3" t="str">
@@ -10927,9 +9863,6 @@
       <x:c r="H355" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I355" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="356" ht="23" customHeight="1">
       <x:c r="A356" s="3" t="str">
@@ -10956,9 +9889,6 @@
       <x:c r="H356" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I356" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="357" ht="23" customHeight="1">
       <x:c r="A357" s="3" t="str">
@@ -10985,9 +9915,6 @@
       <x:c r="H357" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I357" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="358" ht="23" customHeight="1">
       <x:c r="A358" s="3" t="str">
@@ -11014,9 +9941,6 @@
       <x:c r="H358" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I358" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="359" ht="23" customHeight="1">
       <x:c r="A359" s="3" t="str">
@@ -11043,9 +9967,6 @@
       <x:c r="H359" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I359" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="360" ht="23" customHeight="1">
       <x:c r="A360" s="3" t="str">
@@ -11072,9 +9993,6 @@
       <x:c r="H360" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I360" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="361" ht="23" customHeight="1">
       <x:c r="A361" s="3" t="str">
@@ -11101,9 +10019,6 @@
       <x:c r="H361" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I361" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="362" ht="23" customHeight="1">
       <x:c r="A362" s="3" t="str">
@@ -11130,9 +10045,6 @@
       <x:c r="H362" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I362" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="363" ht="23" customHeight="1">
       <x:c r="A363" s="3" t="str">
@@ -11159,9 +10071,6 @@
       <x:c r="H363" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I363" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="364" ht="23" customHeight="1">
       <x:c r="A364" s="3" t="str">
@@ -11188,9 +10097,6 @@
       <x:c r="H364" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I364" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="365" ht="23" customHeight="1">
       <x:c r="A365" s="3" t="str">
@@ -11217,9 +10123,6 @@
       <x:c r="H365" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I365" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="366" ht="23" customHeight="1">
       <x:c r="A366" s="3" t="str">
@@ -11246,9 +10149,6 @@
       <x:c r="H366" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I366" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="367" ht="23" customHeight="1">
       <x:c r="A367" s="3" t="str">
@@ -11275,9 +10175,6 @@
       <x:c r="H367" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I367" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="368" ht="23" customHeight="1">
       <x:c r="A368" s="3" t="str">
@@ -11304,9 +10201,6 @@
       <x:c r="H368" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I368" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="369" ht="23" customHeight="1">
       <x:c r="A369" s="3" t="str">
@@ -11333,9 +10227,6 @@
       <x:c r="H369" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I369" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="370" ht="23" customHeight="1">
       <x:c r="A370" s="3" t="str">
@@ -11362,9 +10253,6 @@
       <x:c r="H370" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I370" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="371" ht="23" customHeight="1">
       <x:c r="A371" s="3" t="str">
@@ -11391,9 +10279,6 @@
       <x:c r="H371" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I371" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="372" ht="23" customHeight="1">
       <x:c r="A372" s="3" t="str">
@@ -11420,9 +10305,6 @@
       <x:c r="H372" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I372" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="373" ht="23" customHeight="1">
       <x:c r="A373" s="3" t="str">
@@ -11449,9 +10331,6 @@
       <x:c r="H373" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I373" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="374" ht="23" customHeight="1">
       <x:c r="A374" s="3" t="str">
@@ -11478,9 +10357,6 @@
       <x:c r="H374" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I374" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="375" ht="23" customHeight="1">
       <x:c r="A375" s="3" t="str">
@@ -11507,9 +10383,6 @@
       <x:c r="H375" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I375" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="376" ht="23" customHeight="1">
       <x:c r="A376" s="3" t="str">
@@ -11536,9 +10409,6 @@
       <x:c r="H376" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I376" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="377" ht="23" customHeight="1">
       <x:c r="A377" s="3" t="str">
@@ -11565,9 +10435,6 @@
       <x:c r="H377" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I377" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="378" ht="23" customHeight="1">
       <x:c r="A378" s="3" t="str">
@@ -11594,9 +10461,6 @@
       <x:c r="H378" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I378" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="379" ht="23" customHeight="1">
       <x:c r="A379" s="3" t="str">
@@ -11623,9 +10487,6 @@
       <x:c r="H379" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I379" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="380" ht="23" customHeight="1">
       <x:c r="A380" s="3" t="str">
@@ -11652,9 +10513,6 @@
       <x:c r="H380" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I380" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="381" ht="23" customHeight="1">
       <x:c r="A381" s="3" t="str">
@@ -11681,9 +10539,6 @@
       <x:c r="H381" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I381" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="382" ht="23" customHeight="1">
       <x:c r="A382" s="3" t="str">
@@ -11710,9 +10565,6 @@
       <x:c r="H382" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I382" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="383" ht="23" customHeight="1">
       <x:c r="A383" s="3" t="str">
@@ -11739,9 +10591,6 @@
       <x:c r="H383" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I383" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="384" ht="23" customHeight="1">
       <x:c r="A384" s="3" t="str">
@@ -11768,9 +10617,6 @@
       <x:c r="H384" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I384" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="385" ht="23" customHeight="1">
       <x:c r="A385" s="3" t="str">
@@ -11797,9 +10643,6 @@
       <x:c r="H385" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I385" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="386" ht="23" customHeight="1">
       <x:c r="A386" s="3" t="str">
@@ -11826,9 +10669,6 @@
       <x:c r="H386" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I386" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="387" ht="23" customHeight="1">
       <x:c r="A387" s="3" t="str">
@@ -11855,9 +10695,6 @@
       <x:c r="H387" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I387" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="388" ht="23" customHeight="1">
       <x:c r="A388" s="3" t="str">
@@ -11884,9 +10721,6 @@
       <x:c r="H388" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I388" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="389" ht="23" customHeight="1">
       <x:c r="A389" s="3" t="str">
@@ -11913,9 +10747,6 @@
       <x:c r="H389" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I389" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="390" ht="23" customHeight="1">
       <x:c r="A390" s="3" t="str">
@@ -11942,9 +10773,6 @@
       <x:c r="H390" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I390" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="391" ht="23" customHeight="1">
       <x:c r="A391" s="3" t="str">
@@ -11971,9 +10799,6 @@
       <x:c r="H391" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I391" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="392" ht="23" customHeight="1">
       <x:c r="A392" s="3" t="str">
@@ -12000,9 +10825,6 @@
       <x:c r="H392" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I392" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="393" ht="23" customHeight="1">
       <x:c r="A393" s="3" t="str">
@@ -12029,9 +10851,6 @@
       <x:c r="H393" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I393" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="394" ht="23" customHeight="1">
       <x:c r="A394" s="3" t="str">
@@ -12058,9 +10877,6 @@
       <x:c r="H394" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I394" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="395" ht="23" customHeight="1">
       <x:c r="A395" s="3" t="str">
@@ -12087,9 +10903,6 @@
       <x:c r="H395" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I395" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="396" ht="23" customHeight="1">
       <x:c r="A396" s="3" t="str">
@@ -12116,9 +10929,6 @@
       <x:c r="H396" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I396" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="397" ht="23" customHeight="1">
       <x:c r="A397" s="3" t="str">
@@ -12145,9 +10955,6 @@
       <x:c r="H397" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I397" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="398" ht="23" customHeight="1">
       <x:c r="A398" s="3" t="str">
@@ -12174,9 +10981,6 @@
       <x:c r="H398" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I398" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="399" ht="23" customHeight="1">
       <x:c r="A399" s="3" t="str">
@@ -12203,9 +11007,6 @@
       <x:c r="H399" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I399" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="400" ht="23" customHeight="1">
       <x:c r="A400" s="3" t="str">
@@ -12232,9 +11033,6 @@
       <x:c r="H400" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I400" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="401" ht="23" customHeight="1">
       <x:c r="A401" s="3" t="str">
@@ -12261,9 +11059,6 @@
       <x:c r="H401" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I401" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="402" ht="23" customHeight="1">
       <x:c r="A402" s="3" t="str">
@@ -12290,9 +11085,6 @@
       <x:c r="H402" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I402" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="403" ht="23" customHeight="1">
       <x:c r="A403" s="3" t="str">
@@ -12319,9 +11111,6 @@
       <x:c r="H403" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I403" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="404" ht="23" customHeight="1">
       <x:c r="A404" s="3" t="str">
@@ -12348,9 +11137,6 @@
       <x:c r="H404" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I404" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="405" ht="23" customHeight="1">
       <x:c r="A405" s="3" t="str">
@@ -12377,9 +11163,6 @@
       <x:c r="H405" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I405" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="406" ht="23" customHeight="1">
       <x:c r="A406" s="3" t="str">
@@ -12406,9 +11189,6 @@
       <x:c r="H406" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I406" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="407" ht="23" customHeight="1">
       <x:c r="A407" s="3" t="str">
@@ -12435,9 +11215,6 @@
       <x:c r="H407" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I407" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="408" ht="23" customHeight="1">
       <x:c r="A408" s="3" t="str">
@@ -12464,9 +11241,6 @@
       <x:c r="H408" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I408" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="409" ht="23" customHeight="1">
       <x:c r="A409" s="3" t="str">
@@ -12493,9 +11267,6 @@
       <x:c r="H409" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I409" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="410" ht="23" customHeight="1">
       <x:c r="A410" s="3" t="str">
@@ -12522,9 +11293,6 @@
       <x:c r="H410" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I410" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="411" ht="23" customHeight="1">
       <x:c r="A411" s="3" t="str">
@@ -12551,9 +11319,6 @@
       <x:c r="H411" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I411" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="412" ht="23" customHeight="1">
       <x:c r="A412" s="3" t="str">
@@ -12580,9 +11345,6 @@
       <x:c r="H412" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I412" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="413" ht="23" customHeight="1">
       <x:c r="A413" s="3" t="str">
@@ -12609,9 +11371,6 @@
       <x:c r="H413" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I413" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="414" ht="23" customHeight="1">
       <x:c r="A414" s="3" t="str">
@@ -12638,9 +11397,6 @@
       <x:c r="H414" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I414" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="415" ht="23" customHeight="1">
       <x:c r="A415" s="3" t="str">
@@ -12667,9 +11423,6 @@
       <x:c r="H415" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I415" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="416" ht="23" customHeight="1">
       <x:c r="A416" s="3" t="str">
@@ -12696,9 +11449,6 @@
       <x:c r="H416" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I416" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="417" ht="23" customHeight="1">
       <x:c r="A417" s="3" t="str">
@@ -12725,9 +11475,6 @@
       <x:c r="H417" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I417" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="418" ht="23" customHeight="1">
       <x:c r="A418" s="3" t="str">
@@ -12754,9 +11501,6 @@
       <x:c r="H418" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I418" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="419" ht="23" customHeight="1">
       <x:c r="A419" s="3" t="str">
@@ -12783,9 +11527,6 @@
       <x:c r="H419" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I419" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="420" ht="23" customHeight="1">
       <x:c r="A420" s="3" t="str">
@@ -12812,9 +11553,6 @@
       <x:c r="H420" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I420" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="421" ht="23" customHeight="1">
       <x:c r="A421" s="3" t="str">
@@ -12841,9 +11579,6 @@
       <x:c r="H421" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I421" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="422" ht="23" customHeight="1">
       <x:c r="A422" s="3" t="str">
@@ -12870,9 +11605,6 @@
       <x:c r="H422" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I422" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="423" ht="23" customHeight="1">
       <x:c r="A423" s="3" t="str">
@@ -12899,9 +11631,6 @@
       <x:c r="H423" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I423" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="424" ht="23" customHeight="1">
       <x:c r="A424" s="3" t="str">
@@ -12928,9 +11657,6 @@
       <x:c r="H424" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I424" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="425" ht="23" customHeight="1">
       <x:c r="A425" s="3" t="str">
@@ -12957,9 +11683,6 @@
       <x:c r="H425" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I425" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="426" ht="23" customHeight="1">
       <x:c r="A426" s="3" t="str">
@@ -12986,9 +11709,6 @@
       <x:c r="H426" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I426" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="427" ht="23" customHeight="1">
       <x:c r="A427" s="3" t="str">
@@ -13015,9 +11735,6 @@
       <x:c r="H427" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I427" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="428" ht="23" customHeight="1">
       <x:c r="A428" s="3" t="str">
@@ -13044,9 +11761,6 @@
       <x:c r="H428" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I428" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="429" ht="23" customHeight="1">
       <x:c r="A429" s="3" t="str">
@@ -13073,9 +11787,6 @@
       <x:c r="H429" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I429" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="430" ht="23" customHeight="1">
       <x:c r="A430" s="3" t="str">
@@ -13102,9 +11813,6 @@
       <x:c r="H430" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I430" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="431" ht="23" customHeight="1">
       <x:c r="A431" s="3" t="str">
@@ -13131,9 +11839,6 @@
       <x:c r="H431" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I431" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="432" ht="23" customHeight="1">
       <x:c r="A432" s="3" t="str">
@@ -13160,9 +11865,6 @@
       <x:c r="H432" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I432" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="433" ht="23" customHeight="1">
       <x:c r="A433" s="3" t="str">
@@ -13189,9 +11891,6 @@
       <x:c r="H433" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I433" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="434" ht="23" customHeight="1">
       <x:c r="A434" s="3" t="str">
@@ -13218,9 +11917,6 @@
       <x:c r="H434" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I434" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="435" ht="23" customHeight="1">
       <x:c r="A435" s="3" t="str">
@@ -13247,9 +11943,6 @@
       <x:c r="H435" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I435" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="436" ht="23" customHeight="1">
       <x:c r="A436" s="3" t="str">
@@ -13276,9 +11969,6 @@
       <x:c r="H436" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I436" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="437" ht="23" customHeight="1">
       <x:c r="A437" s="3" t="str">
@@ -13305,9 +11995,6 @@
       <x:c r="H437" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I437" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="438" ht="23" customHeight="1">
       <x:c r="A438" s="3" t="str">
@@ -13334,9 +12021,6 @@
       <x:c r="H438" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I438" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="439" ht="23" customHeight="1">
       <x:c r="A439" s="3" t="str">
@@ -13363,9 +12047,6 @@
       <x:c r="H439" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I439" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="440" ht="23" customHeight="1">
       <x:c r="A440" s="3" t="str">
@@ -13392,9 +12073,6 @@
       <x:c r="H440" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I440" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="441" ht="23" customHeight="1">
       <x:c r="A441" s="3" t="str">
@@ -13421,9 +12099,6 @@
       <x:c r="H441" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I441" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="442" ht="23" customHeight="1">
       <x:c r="A442" s="3" t="str">
@@ -13450,9 +12125,6 @@
       <x:c r="H442" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I442" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="443" ht="23" customHeight="1">
       <x:c r="A443" s="3" t="str">
@@ -13479,9 +12151,6 @@
       <x:c r="H443" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I443" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="444" ht="23" customHeight="1">
       <x:c r="A444" s="3" t="str">
@@ -13508,9 +12177,6 @@
       <x:c r="H444" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I444" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="445" ht="23" customHeight="1">
       <x:c r="A445" s="3" t="str">
@@ -13537,9 +12203,6 @@
       <x:c r="H445" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I445" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="446" ht="23" customHeight="1">
       <x:c r="A446" s="3" t="str">
@@ -13566,9 +12229,6 @@
       <x:c r="H446" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I446" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="447" ht="23" customHeight="1">
       <x:c r="A447" s="3" t="str">
@@ -13595,9 +12255,6 @@
       <x:c r="H447" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I447" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="448" ht="23" customHeight="1">
       <x:c r="A448" s="3" t="str">
@@ -13624,9 +12281,6 @@
       <x:c r="H448" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I448" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="449" ht="23" customHeight="1">
       <x:c r="A449" s="3" t="str">
@@ -13653,9 +12307,6 @@
       <x:c r="H449" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I449" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="450" ht="23" customHeight="1">
       <x:c r="A450" s="3" t="str">
@@ -13682,9 +12333,6 @@
       <x:c r="H450" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I450" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="451" ht="23" customHeight="1">
       <x:c r="A451" s="3" t="str">
@@ -13711,9 +12359,6 @@
       <x:c r="H451" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I451" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="452" ht="23" customHeight="1">
       <x:c r="A452" s="3" t="str">
@@ -13740,9 +12385,6 @@
       <x:c r="H452" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I452" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="453" ht="23" customHeight="1">
       <x:c r="A453" s="3" t="str">
@@ -13769,9 +12411,6 @@
       <x:c r="H453" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I453" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="454" ht="23" customHeight="1">
       <x:c r="A454" s="3" t="str">
@@ -13798,9 +12437,6 @@
       <x:c r="H454" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I454" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="455" ht="23" customHeight="1">
       <x:c r="A455" s="3" t="str">
@@ -13827,9 +12463,6 @@
       <x:c r="H455" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I455" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="456" ht="23" customHeight="1">
       <x:c r="A456" s="3" t="str">
@@ -13856,9 +12489,6 @@
       <x:c r="H456" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I456" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="457" ht="23" customHeight="1">
       <x:c r="A457" s="3" t="str">
@@ -13885,9 +12515,6 @@
       <x:c r="H457" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I457" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="458" ht="23" customHeight="1">
       <x:c r="A458" s="3" t="str">
@@ -13914,9 +12541,6 @@
       <x:c r="H458" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I458" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="459" ht="23" customHeight="1">
       <x:c r="A459" s="3" t="str">
@@ -13943,9 +12567,6 @@
       <x:c r="H459" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I459" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="460" ht="23" customHeight="1">
       <x:c r="A460" s="3" t="str">
@@ -13972,9 +12593,6 @@
       <x:c r="H460" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I460" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="461" ht="23" customHeight="1">
       <x:c r="A461" s="3" t="str">
@@ -14001,9 +12619,6 @@
       <x:c r="H461" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I461" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="462" ht="23" customHeight="1">
       <x:c r="A462" s="3" t="str">
@@ -14030,9 +12645,6 @@
       <x:c r="H462" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I462" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="463" ht="23" customHeight="1">
       <x:c r="A463" s="3" t="str">
@@ -14059,9 +12671,6 @@
       <x:c r="H463" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I463" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="464" ht="23" customHeight="1">
       <x:c r="A464" s="3" t="str">
@@ -14088,9 +12697,6 @@
       <x:c r="H464" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I464" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="465" ht="23" customHeight="1">
       <x:c r="A465" s="3" t="str">
@@ -14117,9 +12723,6 @@
       <x:c r="H465" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I465" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="466" ht="23" customHeight="1">
       <x:c r="A466" s="3" t="str">
@@ -14146,9 +12749,6 @@
       <x:c r="H466" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I466" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="467" ht="23" customHeight="1">
       <x:c r="A467" s="3" t="str">
@@ -14175,9 +12775,6 @@
       <x:c r="H467" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I467" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="468" ht="23" customHeight="1">
       <x:c r="A468" s="3" t="str">
@@ -14204,9 +12801,6 @@
       <x:c r="H468" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I468" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="469" ht="23" customHeight="1">
       <x:c r="A469" s="3" t="str">
@@ -14233,9 +12827,6 @@
       <x:c r="H469" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I469" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="470" ht="23" customHeight="1">
       <x:c r="A470" s="3" t="str">
@@ -14262,9 +12853,6 @@
       <x:c r="H470" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I470" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="471" ht="23" customHeight="1">
       <x:c r="A471" s="3" t="str">
@@ -14291,9 +12879,6 @@
       <x:c r="H471" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I471" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="472" ht="23" customHeight="1">
       <x:c r="A472" s="3" t="str">
@@ -14320,9 +12905,6 @@
       <x:c r="H472" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I472" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="473" ht="23" customHeight="1">
       <x:c r="A473" s="3" t="str">
@@ -14349,9 +12931,6 @@
       <x:c r="H473" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I473" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="474" ht="23" customHeight="1">
       <x:c r="A474" s="3" t="str">
@@ -14378,9 +12957,6 @@
       <x:c r="H474" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I474" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="475" ht="23" customHeight="1">
       <x:c r="A475" s="3" t="str">
@@ -14407,9 +12983,6 @@
       <x:c r="H475" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I475" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="476" ht="23" customHeight="1">
       <x:c r="A476" s="3" t="str">
@@ -14436,9 +13009,6 @@
       <x:c r="H476" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I476" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="477" ht="23" customHeight="1">
       <x:c r="A477" s="3" t="str">
@@ -14465,9 +13035,6 @@
       <x:c r="H477" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I477" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="478" ht="23" customHeight="1">
       <x:c r="A478" s="3" t="str">
@@ -14494,9 +13061,6 @@
       <x:c r="H478" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I478" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="479" ht="23" customHeight="1">
       <x:c r="A479" s="3" t="str">
@@ -14523,9 +13087,6 @@
       <x:c r="H479" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I479" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="480" ht="23" customHeight="1">
       <x:c r="A480" s="3" t="str">
@@ -14552,9 +13113,6 @@
       <x:c r="H480" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I480" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="481" ht="23" customHeight="1">
       <x:c r="A481" s="3" t="str">
@@ -14581,9 +13139,6 @@
       <x:c r="H481" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I481" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="482" ht="23" customHeight="1">
       <x:c r="A482" s="3" t="str">
@@ -14610,9 +13165,6 @@
       <x:c r="H482" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I482" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="483" ht="23" customHeight="1">
       <x:c r="A483" s="3" t="str">
@@ -14639,9 +13191,6 @@
       <x:c r="H483" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I483" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="484" ht="23" customHeight="1">
       <x:c r="A484" s="3" t="str">
@@ -14668,9 +13217,6 @@
       <x:c r="H484" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I484" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="485" ht="23" customHeight="1">
       <x:c r="A485" s="3" t="str">
@@ -14697,9 +13243,6 @@
       <x:c r="H485" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I485" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="486" ht="23" customHeight="1">
       <x:c r="A486" s="3" t="str">
@@ -14726,9 +13269,6 @@
       <x:c r="H486" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I486" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="487" ht="23" customHeight="1">
       <x:c r="A487" s="3" t="str">
@@ -14755,9 +13295,6 @@
       <x:c r="H487" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I487" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="488" ht="23" customHeight="1">
       <x:c r="A488" s="3" t="str">
@@ -14784,9 +13321,6 @@
       <x:c r="H488" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I488" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="489" ht="23" customHeight="1">
       <x:c r="A489" s="3" t="str">
@@ -14813,9 +13347,6 @@
       <x:c r="H489" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I489" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="490" ht="23" customHeight="1">
       <x:c r="A490" s="3" t="str">
@@ -14842,9 +13373,6 @@
       <x:c r="H490" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I490" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="491" ht="23" customHeight="1">
       <x:c r="A491" s="3" t="str">
@@ -14871,9 +13399,6 @@
       <x:c r="H491" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I491" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="492" ht="23" customHeight="1">
       <x:c r="A492" s="3" t="str">
@@ -14900,9 +13425,6 @@
       <x:c r="H492" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I492" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="493" ht="23" customHeight="1">
       <x:c r="A493" s="3" t="str">
@@ -14929,9 +13451,6 @@
       <x:c r="H493" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I493" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="494" ht="23" customHeight="1">
       <x:c r="A494" s="3" t="str">
@@ -14958,9 +13477,6 @@
       <x:c r="H494" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I494" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="495" ht="23" customHeight="1">
       <x:c r="A495" s="3" t="str">
@@ -14987,9 +13503,6 @@
       <x:c r="H495" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I495" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="496" ht="23" customHeight="1">
       <x:c r="A496" s="3" t="str">
@@ -15016,9 +13529,6 @@
       <x:c r="H496" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I496" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="497" ht="23" customHeight="1">
       <x:c r="A497" s="3" t="str">
@@ -15045,9 +13555,6 @@
       <x:c r="H497" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I497" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="498" ht="23" customHeight="1">
       <x:c r="A498" s="3" t="str">
@@ -15074,9 +13581,6 @@
       <x:c r="H498" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I498" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="499" ht="23" customHeight="1">
       <x:c r="A499" s="3" t="str">
@@ -15103,9 +13607,6 @@
       <x:c r="H499" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I499" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="500" ht="23" customHeight="1">
       <x:c r="A500" s="3" t="str">
@@ -15132,9 +13633,6 @@
       <x:c r="H500" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I500" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="501" ht="23" customHeight="1">
       <x:c r="A501" s="3" t="str">
@@ -15161,9 +13659,6 @@
       <x:c r="H501" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I501" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="502" ht="23" customHeight="1">
       <x:c r="A502" s="3" t="str">
@@ -15190,9 +13685,6 @@
       <x:c r="H502" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I502" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="503" ht="23" customHeight="1">
       <x:c r="A503" s="3" t="str">
@@ -15219,9 +13711,6 @@
       <x:c r="H503" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I503" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="504" ht="23" customHeight="1">
       <x:c r="A504" s="3" t="str">
@@ -15248,9 +13737,6 @@
       <x:c r="H504" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I504" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="505" ht="23" customHeight="1">
       <x:c r="A505" s="3" t="str">
@@ -15277,9 +13763,6 @@
       <x:c r="H505" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I505" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="506" ht="23" customHeight="1">
       <x:c r="A506" s="3" t="str">
@@ -15306,9 +13789,6 @@
       <x:c r="H506" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I506" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="507" ht="23" customHeight="1">
       <x:c r="A507" s="3" t="str">
@@ -15335,9 +13815,6 @@
       <x:c r="H507" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I507" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="508" ht="23" customHeight="1">
       <x:c r="A508" s="3" t="str">
@@ -15364,9 +13841,6 @@
       <x:c r="H508" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I508" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="509" ht="23" customHeight="1">
       <x:c r="A509" s="3" t="str">
@@ -15393,9 +13867,6 @@
       <x:c r="H509" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I509" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="510" ht="23" customHeight="1">
       <x:c r="A510" s="3" t="str">
@@ -15422,9 +13893,6 @@
       <x:c r="H510" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I510" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="511" ht="23" customHeight="1">
       <x:c r="A511" s="3" t="str">
@@ -15451,9 +13919,6 @@
       <x:c r="H511" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I511" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="512" ht="23" customHeight="1">
       <x:c r="A512" s="3" t="str">
@@ -15480,9 +13945,6 @@
       <x:c r="H512" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I512" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="513" ht="23" customHeight="1">
       <x:c r="A513" s="3" t="str">
@@ -15509,9 +13971,6 @@
       <x:c r="H513" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I513" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="514" ht="23" customHeight="1">
       <x:c r="A514" s="3" t="str">
@@ -15538,9 +13997,6 @@
       <x:c r="H514" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I514" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="515" ht="23" customHeight="1">
       <x:c r="A515" s="3" t="str">
@@ -15567,9 +14023,6 @@
       <x:c r="H515" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I515" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="516" ht="23" customHeight="1">
       <x:c r="A516" s="3" t="str">
@@ -15596,9 +14049,6 @@
       <x:c r="H516" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I516" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="517" ht="23" customHeight="1">
       <x:c r="A517" s="3" t="str">
@@ -15625,9 +14075,6 @@
       <x:c r="H517" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I517" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="518" ht="23" customHeight="1">
       <x:c r="A518" s="3" t="str">
@@ -15654,14 +14101,11 @@
       <x:c r="H518" s="3" t="str">
         <x:v>Хабаровск</x:v>
       </x:c>
-      <x:c r="I518" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e7450c0adf047c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4819fc98885541c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16456,7 +14900,7 @@
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="12"/>
       <x:c r="B37" s="25" t="str">
-        <x:v>Детальные записи смоделированы. Итоговые показатели — из презентации проекта.</x:v>
+        <x:v>Учёт посещений. Один человек мог посетить несколько мероприятий.</x:v>
       </x:c>
       <x:c r="C37" s="12"/>
       <x:c r="D37" s="12"/>
@@ -16475,7 +14919,7 @@
     <x:row r="38" ht="25" customHeight="1">
       <x:c r="A38" s="12"/>
       <x:c r="B38" s="25" t="str">
-        <x:v>Учёт посещений. Один человек мог посетить несколько мероприятий.</x:v>
+        <x:v>На фестивале молодёжи 27 июня учтено 326 посещений.</x:v>
       </x:c>
       <x:c r="C38" s="12"/>
       <x:c r="D38" s="12"/>
@@ -16493,9 +14937,7 @@
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="12"/>
-      <x:c r="B39" s="25" t="str">
-        <x:v>На фестивале молодёжи 27 июня учтено 326 посещений.</x:v>
-      </x:c>
+      <x:c r="B39" s="12"/>
       <x:c r="C39" s="12"/>
       <x:c r="D39" s="12"/>
       <x:c r="E39" s="12"/>
@@ -16597,6 +15039,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279d46f39a874f0a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R928e1a67436c4b1d"/>
 </x:worksheet>
 </file>